--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/62.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/62.xlsx
@@ -426,13 +426,13 @@
         <v>-2.52682184041993</v>
       </c>
       <c r="E2">
-        <v>-8.549570807280915</v>
+        <v>-8.028927622145046</v>
       </c>
       <c r="F2">
-        <v>-1.755777872994839</v>
+        <v>-2.148707323573562</v>
       </c>
       <c r="G2">
-        <v>-5.35553356991258</v>
+        <v>-6.165428741185422</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.435599724795989</v>
       </c>
       <c r="E3">
-        <v>-9.179060393665148</v>
+        <v>-7.236091449830135</v>
       </c>
       <c r="F3">
-        <v>-1.77456773079254</v>
+        <v>-1.859551599380547</v>
       </c>
       <c r="G3">
-        <v>-5.786179265297593</v>
+        <v>-5.723159720412027</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.513067738554007</v>
       </c>
       <c r="E4">
-        <v>-9.362708128572212</v>
+        <v>-9.034638300612524</v>
       </c>
       <c r="F4">
-        <v>-1.59769472294679</v>
+        <v>-1.610206384198674</v>
       </c>
       <c r="G4">
-        <v>-6.337159980489576</v>
+        <v>-6.148955466582009</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.774353338746991</v>
       </c>
       <c r="E5">
-        <v>-9.43230171712209</v>
+        <v>-9.548457075418835</v>
       </c>
       <c r="F5">
-        <v>-1.737914129953468</v>
+        <v>-1.625740758103373</v>
       </c>
       <c r="G5">
-        <v>-5.533200617368646</v>
+        <v>-6.171000389328015</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.193817568422424</v>
       </c>
       <c r="E6">
-        <v>-10.16219662920439</v>
+        <v>-11.05358145287422</v>
       </c>
       <c r="F6">
-        <v>-1.483618591172464</v>
+        <v>-1.91042329832127</v>
       </c>
       <c r="G6">
-        <v>-6.264099550983399</v>
+        <v>-6.37365874506004</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.731602255222058</v>
       </c>
       <c r="E7">
-        <v>-12.16204320657574</v>
+        <v>-10.84497729771089</v>
       </c>
       <c r="F7">
-        <v>-0.922822143151227</v>
+        <v>-1.239169855708539</v>
       </c>
       <c r="G7">
-        <v>-6.767673254053018</v>
+        <v>-6.575982735692599</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.33775348077942</v>
       </c>
       <c r="E8">
-        <v>-11.90118951831191</v>
+        <v>-11.16997229181937</v>
       </c>
       <c r="F8">
-        <v>-0.950305716841309</v>
+        <v>-1.415256742889032</v>
       </c>
       <c r="G8">
-        <v>-6.94481723531388</v>
+        <v>-6.508765419063237</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.948189264938032</v>
       </c>
       <c r="E9">
-        <v>-13.15076757904045</v>
+        <v>-12.77390797212212</v>
       </c>
       <c r="F9">
-        <v>-1.064068725737376</v>
+        <v>-1.002393459129342</v>
       </c>
       <c r="G9">
-        <v>-6.811329418079388</v>
+        <v>-7.490368655821458</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.488885107426039</v>
       </c>
       <c r="E10">
-        <v>-13.52263680760232</v>
+        <v>-13.39729770401802</v>
       </c>
       <c r="F10">
-        <v>-0.5271847595327523</v>
+        <v>-0.7897159270323885</v>
       </c>
       <c r="G10">
-        <v>-7.95068677087496</v>
+        <v>-7.484412984396309</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.887301084956986</v>
       </c>
       <c r="E11">
-        <v>-13.37966382623216</v>
+        <v>-14.28989163024791</v>
       </c>
       <c r="F11">
-        <v>-0.5079045082325938</v>
+        <v>-0.5286973584102642</v>
       </c>
       <c r="G11">
-        <v>-7.935292734117348</v>
+        <v>-7.723801842886548</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.079863953727494</v>
       </c>
       <c r="E12">
-        <v>-14.58595873239539</v>
+        <v>-14.17910251365025</v>
       </c>
       <c r="F12">
-        <v>-0.08703588189224901</v>
+        <v>-0.1910771709490613</v>
       </c>
       <c r="G12">
-        <v>-7.999530559761366</v>
+        <v>-7.187526570980008</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.023013232798995</v>
       </c>
       <c r="E13">
-        <v>-14.41101472453106</v>
+        <v>-15.60686696963261</v>
       </c>
       <c r="F13">
-        <v>0.2827266175323803</v>
+        <v>-0.1571074804950592</v>
       </c>
       <c r="G13">
-        <v>-8.253396433894839</v>
+        <v>-7.819920222073748</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.704272071759212</v>
       </c>
       <c r="E14">
-        <v>-14.80040009055461</v>
+        <v>-16.0087373384953</v>
       </c>
       <c r="F14">
-        <v>0.545234590744738</v>
+        <v>0.5761981358939807</v>
       </c>
       <c r="G14">
-        <v>-7.533462027106151</v>
+        <v>-7.682708041107574</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.143050578763815</v>
       </c>
       <c r="E15">
-        <v>-15.94005850169497</v>
+        <v>-16.46271232929024</v>
       </c>
       <c r="F15">
-        <v>0.7244676173210642</v>
+        <v>0.5771209371806995</v>
       </c>
       <c r="G15">
-        <v>-7.728456469914763</v>
+        <v>-7.040293368666461</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.390469558477879</v>
       </c>
       <c r="E16">
-        <v>-16.28591617555679</v>
+        <v>-16.67727142777366</v>
       </c>
       <c r="F16">
-        <v>0.7734556087878214</v>
+        <v>0.7122533399667855</v>
       </c>
       <c r="G16">
-        <v>-7.263308268919465</v>
+        <v>-6.127854049314694</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.526613002277662</v>
       </c>
       <c r="E17">
-        <v>-17.43984380829531</v>
+        <v>-17.96630155405703</v>
       </c>
       <c r="F17">
-        <v>1.100533164313595</v>
+        <v>0.7577563897699652</v>
       </c>
       <c r="G17">
-        <v>-6.059987865759634</v>
+        <v>-6.125970348902849</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.642300016205869</v>
       </c>
       <c r="E18">
-        <v>-17.75396140783737</v>
+        <v>-19.05534973968767</v>
       </c>
       <c r="F18">
-        <v>1.416081502327205</v>
+        <v>1.193174461173081</v>
       </c>
       <c r="G18">
-        <v>-5.911149048859541</v>
+        <v>-5.835986422935928</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.825108815497631</v>
       </c>
       <c r="E19">
-        <v>-18.05989605484756</v>
+        <v>-19.57652275628243</v>
       </c>
       <c r="F19">
-        <v>1.438825157738468</v>
+        <v>1.529528074875403</v>
       </c>
       <c r="G19">
-        <v>-4.884366797126886</v>
+        <v>-4.778157875135988</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.148090010394964</v>
       </c>
       <c r="E20">
-        <v>-19.54873151129736</v>
+        <v>-19.12624752875175</v>
       </c>
       <c r="F20">
-        <v>1.212382644509195</v>
+        <v>1.782731825419517</v>
       </c>
       <c r="G20">
-        <v>-4.09088531063775</v>
+        <v>-4.395419084249768</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6556435526808576</v>
       </c>
       <c r="E21">
-        <v>-20.06243254577947</v>
+        <v>-20.97897304256191</v>
       </c>
       <c r="F21">
-        <v>1.481040417319937</v>
+        <v>1.951508370270305</v>
       </c>
       <c r="G21">
-        <v>-3.567527787425447</v>
+        <v>-3.549104601499403</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.3694386134896491</v>
       </c>
       <c r="E22">
-        <v>-20.89236144869121</v>
+        <v>-21.58835167587808</v>
       </c>
       <c r="F22">
-        <v>2.230376599687953</v>
+        <v>1.694121364342054</v>
       </c>
       <c r="G22">
-        <v>-3.057197260910176</v>
+        <v>-3.505739765480489</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.2873980645029302</v>
       </c>
       <c r="E23">
-        <v>-21.2607573376892</v>
+        <v>-22.10618267865519</v>
       </c>
       <c r="F23">
-        <v>1.878310513089329</v>
+        <v>1.826733045121421</v>
       </c>
       <c r="G23">
-        <v>-2.136584204621947</v>
+        <v>-2.439896386929973</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.3834452456082719</v>
       </c>
       <c r="E24">
-        <v>-20.66969185326005</v>
+        <v>-23.24360402363576</v>
       </c>
       <c r="F24">
-        <v>2.1383366975629</v>
+        <v>2.115737178079724</v>
       </c>
       <c r="G24">
-        <v>-1.684330578502111</v>
+        <v>-2.615196394325462</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.6249474611493334</v>
       </c>
       <c r="E25">
-        <v>-22.67682474530974</v>
+        <v>-23.69278788893059</v>
       </c>
       <c r="F25">
-        <v>2.220355010848884</v>
+        <v>2.302149664936113</v>
       </c>
       <c r="G25">
-        <v>-1.741758611971848</v>
+        <v>-2.914784212901808</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.9711530574971771</v>
       </c>
       <c r="E26">
-        <v>-22.48836324253253</v>
+        <v>-24.32579609961878</v>
       </c>
       <c r="F26">
-        <v>1.919039681550175</v>
+        <v>2.383644450023529</v>
       </c>
       <c r="G26">
-        <v>-1.273988458909447</v>
+        <v>-2.307418286084959</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.377485093274866</v>
       </c>
       <c r="E27">
-        <v>-23.053639067488</v>
+        <v>-24.67246437032797</v>
       </c>
       <c r="F27">
-        <v>2.179137105620387</v>
+        <v>2.140415899743926</v>
       </c>
       <c r="G27">
-        <v>-2.093788782435789</v>
+        <v>-1.983888602168603</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.806117443491972</v>
       </c>
       <c r="E28">
-        <v>-23.59895790749166</v>
+        <v>-25.14063612713696</v>
       </c>
       <c r="F28">
-        <v>2.237704337733117</v>
+        <v>2.004429450165554</v>
       </c>
       <c r="G28">
-        <v>-2.264083244975899</v>
+        <v>-3.392154948028095</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.219246518680846</v>
       </c>
       <c r="E29">
-        <v>-23.81879720666803</v>
+        <v>-24.3111646001</v>
       </c>
       <c r="F29">
-        <v>2.157995512766138</v>
+        <v>2.212947749533051</v>
       </c>
       <c r="G29">
-        <v>-1.91744926374097</v>
+        <v>-3.277156527630432</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.584660372964066</v>
       </c>
       <c r="E30">
-        <v>-22.62463861084535</v>
+        <v>-24.04064261982979</v>
       </c>
       <c r="F30">
-        <v>2.10643295541148</v>
+        <v>2.032759615341297</v>
       </c>
       <c r="G30">
-        <v>-2.646755824951334</v>
+        <v>-3.324788656849466</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.877193686532637</v>
       </c>
       <c r="E31">
-        <v>-22.89659158890199</v>
+        <v>-25.72855885060479</v>
       </c>
       <c r="F31">
-        <v>1.937290272168654</v>
+        <v>1.828257241142572</v>
       </c>
       <c r="G31">
-        <v>-2.970123292136265</v>
+        <v>-3.381531407392574</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.076283430561353</v>
       </c>
       <c r="E32">
-        <v>-22.95781202901168</v>
+        <v>-24.38683087229417</v>
       </c>
       <c r="F32">
-        <v>1.729436323458202</v>
+        <v>2.017671731466707</v>
       </c>
       <c r="G32">
-        <v>-2.67747768755577</v>
+        <v>-3.329704816975283</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.16769455297177</v>
       </c>
       <c r="E33">
-        <v>-23.00258505152552</v>
+        <v>-24.61942688275014</v>
       </c>
       <c r="F33">
-        <v>1.580174457882565</v>
+        <v>1.687829085550389</v>
       </c>
       <c r="G33">
-        <v>-3.270863180560277</v>
+        <v>-3.520524661858874</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.142400745642879</v>
       </c>
       <c r="E34">
-        <v>-23.05961665317812</v>
+        <v>-24.10640059089517</v>
       </c>
       <c r="F34">
-        <v>1.504738351979225</v>
+        <v>1.772768222298644</v>
       </c>
       <c r="G34">
-        <v>-3.713681751893191</v>
+        <v>-3.996925407142156</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.997336736398323</v>
       </c>
       <c r="E35">
-        <v>-22.72004450123895</v>
+        <v>-23.29668679595367</v>
       </c>
       <c r="F35">
-        <v>1.921405498852571</v>
+        <v>1.587116176718025</v>
       </c>
       <c r="G35">
-        <v>-4.316998881515512</v>
+        <v>-3.84405434577523</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.735131110588314</v>
       </c>
       <c r="E36">
-        <v>-21.94893594721284</v>
+        <v>-24.11910296048669</v>
       </c>
       <c r="F36">
-        <v>1.581657235533576</v>
+        <v>1.446141298639994</v>
       </c>
       <c r="G36">
-        <v>-3.740613039855162</v>
+        <v>-3.973357633448084</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.367378057975228</v>
       </c>
       <c r="E37">
-        <v>-22.72124454685098</v>
+        <v>-23.78626464939692</v>
       </c>
       <c r="F37">
-        <v>1.528848813605107</v>
+        <v>1.277124527242394</v>
       </c>
       <c r="G37">
-        <v>-3.419850972009638</v>
+        <v>-3.162214386506936</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.913612593303284</v>
       </c>
       <c r="E38">
-        <v>-21.96230853095749</v>
+        <v>-22.61033768992913</v>
       </c>
       <c r="F38">
-        <v>1.395730171975227</v>
+        <v>1.441480903631843</v>
       </c>
       <c r="G38">
-        <v>-3.535955114617418</v>
+        <v>-3.389188699224908</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.399947551527926</v>
       </c>
       <c r="E39">
-        <v>-22.14589286722845</v>
+        <v>-23.64148480689769</v>
       </c>
       <c r="F39">
-        <v>1.574041225632237</v>
+        <v>1.181134969340792</v>
       </c>
       <c r="G39">
-        <v>-2.788867613315628</v>
+        <v>-3.433506972359131</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.8592363706840578</v>
       </c>
       <c r="E40">
-        <v>-22.25506531860537</v>
+        <v>-22.85671837526445</v>
       </c>
       <c r="F40">
-        <v>1.330683450037798</v>
+        <v>0.7695308040333574</v>
       </c>
       <c r="G40">
-        <v>-3.328559368218695</v>
+        <v>-3.024009041878982</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.3238845777779016</v>
       </c>
       <c r="E41">
-        <v>-21.12435064363016</v>
+        <v>-21.91920198687848</v>
       </c>
       <c r="F41">
-        <v>1.202470400167297</v>
+        <v>1.132006155415559</v>
       </c>
       <c r="G41">
-        <v>-2.88265867898872</v>
+        <v>-2.687862868912464</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.1742465942492625</v>
       </c>
       <c r="E42">
-        <v>-21.59121367145093</v>
+        <v>-21.19306570822254</v>
       </c>
       <c r="F42">
-        <v>1.108712464048837</v>
+        <v>1.234816490511812</v>
       </c>
       <c r="G42">
-        <v>-3.170755593998256</v>
+        <v>-3.695645899795242</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.6086688550056484</v>
       </c>
       <c r="E43">
-        <v>-20.90822469314008</v>
+        <v>-22.21589401843902</v>
       </c>
       <c r="F43">
-        <v>1.239145538558842</v>
+        <v>1.011074455015665</v>
       </c>
       <c r="G43">
-        <v>-3.653201395436246</v>
+        <v>-2.648341576264645</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.959962270616704</v>
       </c>
       <c r="E44">
-        <v>-20.20803204207409</v>
+        <v>-22.11075643740293</v>
       </c>
       <c r="F44">
-        <v>0.9027770142432691</v>
+        <v>0.8155913450986211</v>
       </c>
       <c r="G44">
-        <v>-2.784974411761445</v>
+        <v>-2.18885771868704</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.211477487269336</v>
       </c>
       <c r="E45">
-        <v>-19.26204287881977</v>
+        <v>-21.1218373405559</v>
       </c>
       <c r="F45">
-        <v>1.259250015424786</v>
+        <v>1.200359720024963</v>
       </c>
       <c r="G45">
-        <v>-2.836592437809761</v>
+        <v>-2.242160812414845</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.356904923815115</v>
       </c>
       <c r="E46">
-        <v>-19.73617410742285</v>
+        <v>-21.53035550926185</v>
       </c>
       <c r="F46">
-        <v>0.6900539219391616</v>
+        <v>0.6359764411496043</v>
       </c>
       <c r="G46">
-        <v>-2.932826686090836</v>
+        <v>-2.014871997870642</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.401274824943574</v>
       </c>
       <c r="E47">
-        <v>-19.86851876029702</v>
+        <v>-20.39980838782492</v>
       </c>
       <c r="F47">
-        <v>0.8775532268280241</v>
+        <v>0.6988362731436419</v>
       </c>
       <c r="G47">
-        <v>-2.37213945137771</v>
+        <v>-2.25985236777671</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.357585447841275</v>
       </c>
       <c r="E48">
-        <v>-19.26444297004383</v>
+        <v>-20.93807186532463</v>
       </c>
       <c r="F48">
-        <v>1.044310211950787</v>
+        <v>0.6576167111803386</v>
       </c>
       <c r="G48">
-        <v>-2.288127737227625</v>
+        <v>-2.071419426226933</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.248045761531065</v>
       </c>
       <c r="E49">
-        <v>-19.31288858497789</v>
+        <v>-19.70641297624444</v>
       </c>
       <c r="F49">
-        <v>0.8207255662611724</v>
+        <v>0.4013413743066443</v>
       </c>
       <c r="G49">
-        <v>-2.511748467314316</v>
+        <v>-2.064291821680883</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.100691118063716</v>
       </c>
       <c r="E50">
-        <v>-19.1824187203429</v>
+        <v>-19.26528073773525</v>
       </c>
       <c r="F50">
-        <v>0.6494282994036654</v>
+        <v>0.6050369186550427</v>
       </c>
       <c r="G50">
-        <v>-2.659233271088847</v>
+        <v>-1.440336751166746</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.9440865422554756</v>
       </c>
       <c r="E51">
-        <v>-19.18057110294777</v>
+        <v>-19.2947112903111</v>
       </c>
       <c r="F51">
-        <v>0.6141754678427269</v>
+        <v>0.2837330839267817</v>
       </c>
       <c r="G51">
-        <v>-2.422400153754925</v>
+        <v>-1.951928595532479</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.8058136588295032</v>
       </c>
       <c r="E52">
-        <v>-18.46211058773484</v>
+        <v>-19.01044991990162</v>
       </c>
       <c r="F52">
-        <v>0.1584392007837453</v>
+        <v>0.4078573122970652</v>
       </c>
       <c r="G52">
-        <v>-2.556348136819377</v>
+        <v>-2.303631021988032</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.7103496946303831</v>
       </c>
       <c r="E53">
-        <v>-17.44236163984358</v>
+        <v>-18.81929397508983</v>
       </c>
       <c r="F53">
-        <v>0.3183190797284667</v>
+        <v>0.3301390541990128</v>
       </c>
       <c r="G53">
-        <v>-1.986543659691099</v>
+        <v>-1.557013618152819</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.6736608114459427</v>
       </c>
       <c r="E54">
-        <v>-17.73952010422691</v>
+        <v>-19.12220812993692</v>
       </c>
       <c r="F54">
-        <v>0.486049396549519</v>
+        <v>0.2105592494004874</v>
       </c>
       <c r="G54">
-        <v>-2.265112824638612</v>
+        <v>-2.90141954055977</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.7017051175552557</v>
       </c>
       <c r="E55">
-        <v>-17.71971708739137</v>
+        <v>-17.86791139929238</v>
       </c>
       <c r="F55">
-        <v>-0.02263280142679585</v>
+        <v>-0.1693640045868807</v>
       </c>
       <c r="G55">
-        <v>-2.007227948220465</v>
+        <v>-3.033626176670565</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.7919658457334688</v>
       </c>
       <c r="E56">
-        <v>-17.26018565898901</v>
+        <v>-17.95424675624861</v>
       </c>
       <c r="F56">
-        <v>0.06831117062435348</v>
+        <v>-0.02943369780377978</v>
       </c>
       <c r="G56">
-        <v>-2.604695343874893</v>
+        <v>-2.034682302377641</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.9324645568010124</v>
       </c>
       <c r="E57">
-        <v>-17.79310553715967</v>
+        <v>-16.16352510855148</v>
       </c>
       <c r="F57">
-        <v>-0.1612302650587923</v>
+        <v>-0.2150070484811334</v>
       </c>
       <c r="G57">
-        <v>-2.300303923721065</v>
+        <v>-2.663573396290831</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.103932961256078</v>
       </c>
       <c r="E58">
-        <v>-17.80353008432533</v>
+        <v>-16.19220393444206</v>
       </c>
       <c r="F58">
-        <v>-0.2018277231025933</v>
+        <v>-0.1926668079950336</v>
       </c>
       <c r="G58">
-        <v>-2.874872275880354</v>
+        <v>-2.818069935517539</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.283799282975987</v>
       </c>
       <c r="E59">
-        <v>-17.03048787189794</v>
+        <v>-16.86358190539724</v>
       </c>
       <c r="F59">
-        <v>0.1847995082756312</v>
+        <v>-0.5585889961402843</v>
       </c>
       <c r="G59">
-        <v>-2.625531917499066</v>
+        <v>-3.676673163309679</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.447072677635447</v>
       </c>
       <c r="E60">
-        <v>-17.19793725527957</v>
+        <v>-16.94978593660725</v>
       </c>
       <c r="F60">
-        <v>-0.3012541773584095</v>
+        <v>-0.1794709152684374</v>
       </c>
       <c r="G60">
-        <v>-2.825535215708596</v>
+        <v>-2.973619228225735</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.56932119865306</v>
       </c>
       <c r="E61">
-        <v>-16.90900249969417</v>
+        <v>-16.3251282319892</v>
       </c>
       <c r="F61">
-        <v>-0.4307495399684451</v>
+        <v>-0.667400853069819</v>
       </c>
       <c r="G61">
-        <v>-2.787401041641731</v>
+        <v>-3.067632100449958</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.629770288789406</v>
       </c>
       <c r="E62">
-        <v>-16.23765169958303</v>
+        <v>-16.97846476249783</v>
       </c>
       <c r="F62">
-        <v>-0.5653675265973928</v>
+        <v>-0.4380085235191771</v>
       </c>
       <c r="G62">
-        <v>-3.669492590035</v>
+        <v>-3.800500808660578</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.61321801702071</v>
       </c>
       <c r="E63">
-        <v>-15.9812857290608</v>
+        <v>-15.83858445613109</v>
       </c>
       <c r="F63">
-        <v>-0.4115761480632477</v>
+        <v>-0.7430713869481511</v>
       </c>
       <c r="G63">
-        <v>-3.986331661416488</v>
+        <v>-3.508858299378483</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.51047426187555</v>
       </c>
       <c r="E64">
-        <v>-15.90255820843745</v>
+        <v>-15.18959978914384</v>
       </c>
       <c r="F64">
-        <v>-0.4555715691933322</v>
+        <v>-0.672019829707829</v>
       </c>
       <c r="G64">
-        <v>-3.969209519887377</v>
+        <v>-4.256846269066954</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.320916101880657</v>
       </c>
       <c r="E65">
-        <v>-16.17722374242468</v>
+        <v>-15.04675360504588</v>
       </c>
       <c r="F65">
-        <v>-0.6360811099373725</v>
+        <v>-0.6046892988408825</v>
       </c>
       <c r="G65">
-        <v>-4.346548810999046</v>
+        <v>-3.836536096855545</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.051792789196491</v>
       </c>
       <c r="E66">
-        <v>-15.97982756043033</v>
+        <v>-15.8947918755143</v>
       </c>
       <c r="F66">
-        <v>-0.5817203274960577</v>
+        <v>-0.7825729149180483</v>
       </c>
       <c r="G66">
-        <v>-4.096238462774751</v>
+        <v>-4.438773988632063</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.7159298945832788</v>
       </c>
       <c r="E67">
-        <v>-16.01437528863485</v>
+        <v>-15.28639592105779</v>
       </c>
       <c r="F67">
-        <v>-0.7025310862551433</v>
+        <v>-0.5469926808684941</v>
       </c>
       <c r="G67">
-        <v>-4.688958536125865</v>
+        <v>-4.078967346696374</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.3336925815711551</v>
       </c>
       <c r="E68">
-        <v>-15.68592054038451</v>
+        <v>-15.64263285734519</v>
       </c>
       <c r="F68">
-        <v>-0.7483108107708579</v>
+        <v>-0.8521276122615116</v>
       </c>
       <c r="G68">
-        <v>-4.698535944370977</v>
+        <v>-4.708825119907032</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.07158012713987257</v>
       </c>
       <c r="E69">
-        <v>-15.56629637099789</v>
+        <v>-15.41887642815219</v>
       </c>
       <c r="F69">
-        <v>-0.9721133170874088</v>
+        <v>-0.9418265481062532</v>
       </c>
       <c r="G69">
-        <v>-4.445805587357475</v>
+        <v>-4.954368282554776</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.4758580918706246</v>
       </c>
       <c r="E70">
-        <v>-15.75076828817435</v>
+        <v>-13.88230632718754</v>
       </c>
       <c r="F70">
-        <v>-0.9760132708197888</v>
+        <v>-1.159675577898884</v>
       </c>
       <c r="G70">
-        <v>-4.553828688303894</v>
+        <v>-4.871074956786712</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.8556500007528005</v>
       </c>
       <c r="E71">
-        <v>-16.32223906557231</v>
+        <v>-15.26911979271853</v>
       </c>
       <c r="F71">
-        <v>-0.9661449299502384</v>
+        <v>-1.127392443476982</v>
       </c>
       <c r="G71">
-        <v>-4.772748443724819</v>
+        <v>-3.856329848634847</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.194069936298351</v>
       </c>
       <c r="E72">
-        <v>-15.45532158696592</v>
+        <v>-14.90201451881272</v>
       </c>
       <c r="F72">
-        <v>-0.7350734996741218</v>
+        <v>-0.9768880267971451</v>
       </c>
       <c r="G72">
-        <v>-4.58209743666373</v>
+        <v>-4.868843649093243</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.479653771199748</v>
       </c>
       <c r="E73">
-        <v>-15.85613229291081</v>
+        <v>-15.70171132924925</v>
       </c>
       <c r="F73">
-        <v>-1.186194103564705</v>
+        <v>-1.191925577624674</v>
       </c>
       <c r="G73">
-        <v>-4.005979749192062</v>
+        <v>-4.338755786799602</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.707576856110524</v>
       </c>
       <c r="E74">
-        <v>-16.95563672502516</v>
+        <v>-16.06347753230002</v>
       </c>
       <c r="F74">
-        <v>-1.066434543039772</v>
+        <v>-1.188506905353321</v>
       </c>
       <c r="G74">
-        <v>-4.345155071327013</v>
+        <v>-4.707666428968286</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.882136616827973</v>
       </c>
       <c r="E75">
-        <v>-16.17415796552149</v>
+        <v>-16.00015588025076</v>
       </c>
       <c r="F75">
-        <v>-1.272169527933863</v>
+        <v>-1.379729721717767</v>
       </c>
       <c r="G75">
-        <v>-3.89833405043712</v>
+        <v>-4.880109435563384</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.011290185681294</v>
       </c>
       <c r="E76">
-        <v>-16.54207836474867</v>
+        <v>-15.66265776940711</v>
       </c>
       <c r="F76">
-        <v>-1.308625148963666</v>
+        <v>-1.411230877311427</v>
       </c>
       <c r="G76">
-        <v>-3.744552589046895</v>
+        <v>-4.139917800619896</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.105173160828663</v>
       </c>
       <c r="E77">
-        <v>-17.18287555073006</v>
+        <v>-17.00831193468238</v>
       </c>
       <c r="F77">
-        <v>-1.261674112940393</v>
+        <v>-1.273424504549104</v>
       </c>
       <c r="G77">
-        <v>-3.437532595734885</v>
+        <v>-4.639419532676211</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.178442184042904</v>
       </c>
       <c r="E78">
-        <v>-17.15110377709225</v>
+        <v>-16.24591616464703</v>
       </c>
       <c r="F78">
-        <v>-1.497096128816012</v>
+        <v>-1.527734125575955</v>
       </c>
       <c r="G78">
-        <v>-3.958324446154253</v>
+        <v>-4.048702339376357</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.244366565063568</v>
       </c>
       <c r="E79">
-        <v>-18.09056740930151</v>
+        <v>-17.82909332009863</v>
       </c>
       <c r="F79">
-        <v>-1.25968188933666</v>
+        <v>-1.582326850890053</v>
       </c>
       <c r="G79">
-        <v>-3.655469119130647</v>
+        <v>-4.010740313677534</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.31319933469707</v>
       </c>
       <c r="E80">
-        <v>-17.69539012502216</v>
+        <v>-18.40455368309735</v>
       </c>
       <c r="F80">
-        <v>-1.517633013466218</v>
+        <v>-1.325579344596763</v>
       </c>
       <c r="G80">
-        <v>-2.806741248682153</v>
+        <v>-3.185957619114589</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.395663366565015</v>
       </c>
       <c r="E81">
-        <v>-18.61176306826632</v>
+        <v>-18.76127063762955</v>
       </c>
       <c r="F81">
-        <v>-1.848842465597155</v>
+        <v>-1.469884259634048</v>
       </c>
       <c r="G81">
-        <v>-3.218056668663363</v>
+        <v>-2.57745617517777</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.496951301003528</v>
       </c>
       <c r="E82">
-        <v>-20.76103117399476</v>
+        <v>-19.56109877381231</v>
       </c>
       <c r="F82">
-        <v>-1.478585430833055</v>
+        <v>-1.820331716327602</v>
       </c>
       <c r="G82">
-        <v>-3.077179713785216</v>
+        <v>-3.246414801752759</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.618091496517352</v>
       </c>
       <c r="E83">
-        <v>-20.81922206499333</v>
+        <v>-20.96543290527898</v>
       </c>
       <c r="F83">
-        <v>-1.507140911942359</v>
+        <v>-1.272120654257097</v>
       </c>
       <c r="G83">
-        <v>-3.392598561130357</v>
+        <v>-3.243124119486724</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.759850532836552</v>
       </c>
       <c r="E84">
-        <v>-21.88309193514132</v>
+        <v>-21.26791685509533</v>
       </c>
       <c r="F84">
-        <v>-1.604654665865111</v>
+        <v>-1.632312196709781</v>
       </c>
       <c r="G84">
-        <v>-2.966230090582082</v>
+        <v>-2.838102046575669</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.917527265440184</v>
       </c>
       <c r="E85">
-        <v>-22.64870745019612</v>
+        <v>-22.3759936885062</v>
       </c>
       <c r="F85">
-        <v>-1.469595159410471</v>
+        <v>-1.771076990557143</v>
       </c>
       <c r="G85">
-        <v>-3.244517859158757</v>
+        <v>-3.157165804559547</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.084308044818976</v>
       </c>
       <c r="E86">
-        <v>-23.40560112431215</v>
+        <v>-23.70019647240714</v>
       </c>
       <c r="F86">
-        <v>-1.702686977782016</v>
+        <v>-1.700796643368828</v>
       </c>
       <c r="G86">
-        <v>-2.637410154893971</v>
+        <v>-2.439310420369523</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.255114427620641</v>
       </c>
       <c r="E87">
-        <v>-24.47250054357127</v>
+        <v>-24.69471729160166</v>
       </c>
       <c r="F87">
-        <v>-1.678159847352525</v>
+        <v>-1.84263302354577</v>
       </c>
       <c r="G87">
-        <v>-2.50741496320341</v>
+        <v>-2.119233635450627</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.421228891339311</v>
       </c>
       <c r="E88">
-        <v>-26.177964611126</v>
+        <v>-25.5284229418358</v>
       </c>
       <c r="F88">
-        <v>-1.525731133195986</v>
+        <v>-1.582731922550022</v>
       </c>
       <c r="G88">
-        <v>-2.925778534637727</v>
+        <v>-2.92317644584386</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.577217206395698</v>
       </c>
       <c r="E89">
-        <v>-27.90732090754519</v>
+        <v>-27.84691106428287</v>
       </c>
       <c r="F89">
-        <v>-2.006740061346977</v>
+        <v>-1.657815972307172</v>
       </c>
       <c r="G89">
-        <v>-2.564743680306969</v>
+        <v>-2.945320684956045</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.720484005741563</v>
       </c>
       <c r="E90">
-        <v>-28.51283675253282</v>
+        <v>-29.05699630319052</v>
       </c>
       <c r="F90">
-        <v>-1.587616805124331</v>
+        <v>-1.545399888808057</v>
       </c>
       <c r="G90">
-        <v>-2.25294988032733</v>
+        <v>-3.411587850343617</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.846605668537711</v>
       </c>
       <c r="E91">
-        <v>-30.39441091000884</v>
+        <v>-31.24496701202552</v>
       </c>
       <c r="F91">
-        <v>-1.607103319907787</v>
+        <v>-1.523778671227587</v>
       </c>
       <c r="G91">
-        <v>-2.792489350135591</v>
+        <v>-2.911619331366264</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.956674165625699</v>
       </c>
       <c r="E92">
-        <v>-32.12286377586351</v>
+        <v>-32.60316731453904</v>
       </c>
       <c r="F92">
-        <v>-1.761826611770081</v>
+        <v>-1.448542201868322</v>
       </c>
       <c r="G92">
-        <v>-2.247656318010035</v>
+        <v>-3.540232339454156</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.052923689071921</v>
       </c>
       <c r="E93">
-        <v>-34.05724673297998</v>
+        <v>-34.98444499333947</v>
       </c>
       <c r="F93">
-        <v>-1.555027174763393</v>
+        <v>-1.184495950388966</v>
       </c>
       <c r="G93">
-        <v>-3.373178900996992</v>
+        <v>-4.565978390433019</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.135681719982126</v>
       </c>
       <c r="E94">
-        <v>-36.1122818230828</v>
+        <v>-36.71513039687991</v>
       </c>
       <c r="F94">
-        <v>-1.519037924581366</v>
+        <v>-1.519654229929048</v>
       </c>
       <c r="G94">
-        <v>-3.260233018833678</v>
+        <v>-3.864639317938418</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.211782314319187</v>
       </c>
       <c r="E95">
-        <v>-37.21036657859575</v>
+        <v>-39.56520249766538</v>
       </c>
       <c r="F95">
-        <v>-1.405574784685112</v>
+        <v>-1.314737672028923</v>
       </c>
       <c r="G95">
-        <v>-3.101548639499792</v>
+        <v>-4.978389600987727</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.283347594907172</v>
       </c>
       <c r="E96">
-        <v>-39.72509385792821</v>
+        <v>-40.56366308924658</v>
       </c>
       <c r="F96">
-        <v>-1.414178208530587</v>
+        <v>-1.124547829815768</v>
       </c>
       <c r="G96">
-        <v>-4.017781844039564</v>
+        <v>-4.565322902416243</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.351499999841754</v>
       </c>
       <c r="E97">
-        <v>-41.02645049046046</v>
+        <v>-42.2112079742432</v>
       </c>
       <c r="F97">
-        <v>-1.188182185331423</v>
+        <v>-0.8784465013832575</v>
       </c>
       <c r="G97">
-        <v>-4.099035873755436</v>
+        <v>-4.638171457007906</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.415280799587094</v>
       </c>
       <c r="E98">
-        <v>-43.85822076354393</v>
+        <v>-44.87946637209472</v>
       </c>
       <c r="F98">
-        <v>-1.278635763880115</v>
+        <v>-0.7487059420219934</v>
       </c>
       <c r="G98">
-        <v>-3.510751931426946</v>
+        <v>-5.171033556463457</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.473714750704093</v>
       </c>
       <c r="E99">
-        <v>-45.72368034626366</v>
+        <v>-47.1065087546679</v>
       </c>
       <c r="F99">
-        <v>-1.519699790136202</v>
+        <v>-0.8139630692797327</v>
       </c>
       <c r="G99">
-        <v>-4.768391765795138</v>
+        <v>-5.835443493467488</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.510003024929286</v>
       </c>
       <c r="E100">
-        <v>-48.77755641976432</v>
+        <v>-49.43273151072007</v>
       </c>
       <c r="F100">
-        <v>-1.418049997771272</v>
+        <v>-0.8496582490337663</v>
       </c>
       <c r="G100">
-        <v>-4.847424419454159</v>
+        <v>-5.908050378234783</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.525212019670824</v>
       </c>
       <c r="E101">
-        <v>-50.44539905738183</v>
+        <v>-51.07134284861806</v>
       </c>
       <c r="F101">
-        <v>-1.281015663428358</v>
+        <v>-0.7381160931446045</v>
       </c>
       <c r="G101">
-        <v>-5.031894637993428</v>
+        <v>-6.490136979313758</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.484939155609521</v>
       </c>
       <c r="E102">
-        <v>-53.10961239582599</v>
+        <v>-52.71619102734311</v>
       </c>
       <c r="F102">
-        <v>-1.170808835792509</v>
+        <v>-0.4934743480758265</v>
       </c>
       <c r="G102">
-        <v>-5.722179798932403</v>
+        <v>-6.97602574811259</v>
       </c>
     </row>
   </sheetData>
